--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487632_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487632_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.755</v>
+        <v>6.9335</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1647</v>
+        <v>6.7247</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5903</v>
+        <v>0.2087</v>
       </c>
       <c r="G2" t="n">
         <v>3.6068</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2661</v>
+        <v>-0.5554</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8512</v>
+        <v>0.4113</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.9667</v>
       </c>
       <c r="V2" t="n">
         <v>1.5537</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8308</v>
+        <v>2.9666</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7188</v>
+        <v>1.0181</v>
       </c>
       <c r="F3" t="n">
-        <v>2.112</v>
+        <v>1.9485</v>
       </c>
       <c r="G3" t="n">
         <v>3.3398</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2851</v>
+        <v>0.4209</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3963</v>
+        <v>0.6956</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1112</v>
+        <v>-0.2748</v>
       </c>
       <c r="V3" t="n">
         <v>0.5642</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3025</v>
+        <v>2.4048</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3878</v>
+        <v>1.7081</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9147</v>
+        <v>0.6966</v>
       </c>
       <c r="G4" t="n">
         <v>1.2854</v>
@@ -766,13 +766,13 @@
         <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5034</v>
+        <v>0.6057</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6397</v>
+        <v>0.96</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1363</v>
+        <v>-0.3544</v>
       </c>
       <c r="V4" t="n">
         <v>1.2898</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2192</v>
+        <v>1.4733</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5397</v>
+        <v>-0.5582</v>
       </c>
       <c r="F5" t="n">
-        <v>1.759</v>
+        <v>2.0315</v>
       </c>
       <c r="G5" t="n">
         <v>0.6923</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0913</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3656</v>
+        <v>0.3471</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4569</v>
+        <v>-1.1843</v>
       </c>
       <c r="V5" t="n">
         <v>0.066</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0533</v>
+        <v>0.6773</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.221</v>
+        <v>-0.4608</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2744</v>
+        <v>1.1381</v>
       </c>
       <c r="G6" t="n">
         <v>-0.06320000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4789</v>
+        <v>0.1029</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3645</v>
+        <v>0.1248</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1144</v>
+        <v>-0.0219</v>
       </c>
       <c r="V6" t="n">
         <v>0.4436</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.6923</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0599</v>
+        <v>0.1403</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9144</v>
+        <v>-0.8326</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4898</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.2153</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1211</v>
+        <v>0.0791</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0545</v>
+        <v>0.1363</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6119</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6117</v>
+        <v>-1.0689</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2188</v>
+        <v>0.2421</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3928</v>
+        <v>-1.3111</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6785</v>
@@ -1078,13 +1078,13 @@
         <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5153</v>
+        <v>0.0275</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>0.1581</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6119</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1887</v>
+        <v>-1.7243</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0267</v>
+        <v>-0.4261</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.162</v>
+        <v>-1.2982</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2672</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3095</v>
+        <v>0.1548</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.424</v>
+        <v>0.1766</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1144</v>
+        <v>-0.0219</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2787</v>
+        <v>-1.7999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1807</v>
+        <v>-1.92</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0979</v>
+        <v>0.1201</v>
       </c>
       <c r="G10" t="n">
         <v>-0.769</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2858</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2434</v>
+        <v>0.5041</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5291</v>
+        <v>-1.3111</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6119</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9409</v>
+        <v>-2.9382</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9284</v>
+        <v>-2.0074</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0126</v>
+        <v>-0.9308</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2489</v>
@@ -1312,13 +1312,13 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0296</v>
+        <v>-0.0269</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1828</v>
+        <v>0.1037</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V11" t="n">
         <v>0.1137</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0874</v>
+        <v>-4.781</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2349</v>
+        <v>-3.874</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8525</v>
+        <v>-0.907</v>
       </c>
       <c r="G12" t="n">
         <v>0.7323</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0733</v>
+        <v>0.233</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3028</v>
+        <v>0.058</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2295</v>
+        <v>0.175</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4477</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8498</v>
+        <v>-6.3128</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9392</v>
+        <v>-5.7565</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9106</v>
+        <v>-0.5563</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1379</v>
@@ -1468,13 +1468,13 @@
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2256</v>
+        <v>-0.6886</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7863</v>
+        <v>0.3964</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4394</v>
+        <v>-1.0851</v>
       </c>
       <c r="V13" t="n">
         <v>-0.546</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.770700000000001</v>
+        <v>-4.861899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.077999999999998</v>
+        <v>-5.169699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3075999999999991</v>
+        <v>0.3074999999999994</v>
       </c>
       <c r="G14" t="n">
         <v>0.002100000000000879</v>
@@ -1546,13 +1546,13 @@
         <v>11.6419</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0635</v>
+        <v>-1.155</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1065</v>
+        <v>4.014799999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.1701</v>
+        <v>-5.170299999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7983999999999998</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4545</v>
+        <v>6.6542</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7668</v>
+        <v>3.6667</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6877</v>
+        <v>2.9875</v>
       </c>
       <c r="G15" t="n">
         <v>2.813</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0301</v>
+        <v>0.1696</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8871</v>
+        <v>0.787</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9172</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>3.6716</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.084</v>
+        <v>4.7937</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3497</v>
+        <v>5.9503</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2656</v>
+        <v>-1.1566</v>
       </c>
       <c r="G16" t="n">
         <v>5.0535</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5218</v>
+        <v>0.1879</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2198</v>
+        <v>0.8204</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7416</v>
+        <v>-0.6325</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2239</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5161</v>
+        <v>1.8531</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8377</v>
+        <v>-0.3372</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3538</v>
+        <v>2.1903</v>
       </c>
       <c r="G17" t="n">
         <v>0.408</v>
@@ -1780,13 +1780,13 @@
         <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5218</v>
+        <v>-0.1848</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2894</v>
+        <v>0.2111</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2324</v>
+        <v>-0.3959</v>
       </c>
       <c r="V17" t="n">
         <v>0.6597</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3091</v>
+        <v>0.8359</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1016</v>
+        <v>0.6011</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2075</v>
+        <v>0.2348</v>
       </c>
       <c r="G18" t="n">
         <v>0.4476</v>
@@ -1858,13 +1858,13 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2615</v>
+        <v>-0.2117</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6079</v>
+        <v>0.1074</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3463</v>
+        <v>-0.3191</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5642</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0178</v>
+        <v>-0.1834</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5073</v>
+        <v>-0.6939</v>
       </c>
       <c r="F19" t="n">
         <v>0.5105</v>
@@ -1936,10 +1936,10 @@
         <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5287</v>
+        <v>0.3275</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6386</v>
+        <v>0.4374</v>
       </c>
       <c r="U19" t="n">
         <v>-0.1099</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6261</v>
+        <v>-0.3715</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0493</v>
+        <v>-1.1976</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6753</v>
+        <v>0.826</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0833</v>
+        <v>-0.5322</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0115</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0949</v>
+        <v>-1.2646</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1472</v>
+        <v>-0.6314</v>
       </c>
       <c r="K20" t="n">
-        <v>0.931</v>
+        <v>0.622</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.0781</v>
+        <v>-1.2535</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9362</v>
+        <v>0.0992</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9195</v>
+        <v>0.1104</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0167</v>
+        <v>-0.0111</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>1.893</v>
+        <v>0.1607</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8337</v>
+        <v>0.404</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0592</v>
+        <v>-0.2434</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7183</v>
+        <v>-0.5385</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5019</v>
+        <v>-1.0503</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2164</v>
+        <v>0.5118</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1935</v>
+        <v>-2.0833</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3287</v>
+        <v>0.0115</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8647</v>
+        <v>-2.0949</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2452</v>
+        <v>-1.1472</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0422</v>
+        <v>0.931</v>
       </c>
       <c r="L21" t="n">
-        <v>0.203</v>
+        <v>-2.0781</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0517</v>
+        <v>-0.9362</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7135</v>
+        <v>-0.9195</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.0167</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8062</v>
+        <v>0.7284</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5709</v>
+        <v>0.8327</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2353</v>
+        <v>-0.1043</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5537</v>
+        <v>0.2343</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3776</v>
+        <v>0.2343</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.09</v>
+        <v>-0.5453</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6981</v>
+        <v>-0.3017</v>
       </c>
       <c r="F22" t="n">
-        <v>0.608</v>
+        <v>-0.2436</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5322</v>
+        <v>1.1935</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.3287</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2646</v>
+        <v>0.8647</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6314</v>
+        <v>1.2452</v>
       </c>
       <c r="K22" t="n">
-        <v>0.622</v>
+        <v>1.0422</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2535</v>
+        <v>0.203</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0992</v>
+        <v>-0.0517</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1104</v>
+        <v>-0.7135</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0111</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5579</v>
+        <v>0.9791</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0965</v>
+        <v>0.7711</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4614</v>
+        <v>0.2081</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4596</v>
+        <v>-0.7033</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9277</v>
+        <v>-1.2343</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4681</v>
+        <v>0.531</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5583</v>
+        <v>-2.5097</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6833</v>
+        <v>-2.6249</v>
       </c>
       <c r="I23" t="n">
-        <v>1.125</v>
+        <v>0.1152</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3902</v>
+        <v>-1.8843</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9814</v>
+        <v>-1.7548</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5911999999999999</v>
+        <v>-0.1295</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1681</v>
+        <v>-0.6254</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7019</v>
+        <v>-0.87</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5339</v>
+        <v>0.2447</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1763</v>
+        <v>-0.7458</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1222</v>
+        <v>0.0381</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0541</v>
+        <v>-0.7839</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6597</v>
+        <v>0.6119</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6597</v>
+        <v>0.6119</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5586</v>
+        <v>-1.3323</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0351</v>
+        <v>-1.8276</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4765</v>
+        <v>0.4953</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5097</v>
+        <v>-1.5583</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6249</v>
+        <v>-2.6833</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1152</v>
+        <v>1.125</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8843</v>
+        <v>-1.3902</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.7548</v>
+        <v>-1.9814</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1295</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6254</v>
+        <v>-0.1681</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.87</v>
+        <v>-0.7019</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2447</v>
+        <v>0.5339</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6011</v>
+        <v>0.3037</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7627</v>
+        <v>0.2223</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8385</v>
+        <v>0.0813</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6119</v>
+        <v>-0.6597</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6119</v>
+        <v>-0.6597</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4105</v>
+        <v>-4.692</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9833</v>
+        <v>-3.8832</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4273</v>
+        <v>-0.8088</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8769</v>
@@ -2404,13 +2404,13 @@
         <v>1.3582</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.3491</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4385</v>
+        <v>0.5386</v>
       </c>
       <c r="U25" t="n">
-        <v>0.192</v>
+        <v>-0.1895</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6119</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.770599999999997</v>
+        <v>5.7706</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3076999999999996</v>
       </c>
       <c r="F26" t="n">
-        <v>6.0781</v>
+        <v>6.078200000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.001999999999999336</v>
+        <v>-0.001999999999998892</v>
       </c>
       <c r="H26" t="n">
         <v>-6.7311</v>
@@ -2455,10 +2455,10 @@
         <v>6.728999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9912000000000001</v>
+        <v>0.9911999999999996</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1567000000000003</v>
+        <v>0.1567000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>0.8344999999999999</v>
@@ -2482,13 +2482,13 @@
         <v>14.5524</v>
       </c>
       <c r="S26" t="n">
-        <v>2.0635</v>
+        <v>2.0637</v>
       </c>
       <c r="T26" t="n">
-        <v>5.170100000000001</v>
+        <v>5.1701</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.106699999999999</v>
+        <v>-3.1065</v>
       </c>
       <c r="V26" t="n">
         <v>0.7983999999999999</v>
